--- a/MU/Test upload format/CG fee reduction/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
+++ b/MU/Test upload format/CG fee reduction/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AN$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AN$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="178">
   <si>
     <t>loancat</t>
   </si>
@@ -89,7 +89,7 @@
     <t>sancdt</t>
   </si>
   <si>
-    <t>frstdisamt</t>
+    <t>TotalLoanDisbursedAmount</t>
   </si>
   <si>
     <t>frstdisdt</t>
@@ -155,7 +155,7 @@
     <t>SHG</t>
   </si>
   <si>
-    <t>Port262701part1</t>
+    <t>CR701</t>
   </si>
   <si>
     <t>F</t>
@@ -170,19 +170,10 @@
     <t>124 Main Street</t>
   </si>
   <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>SHG0124234</t>
-  </si>
-  <si>
-    <t>SHG01234</t>
+    <t>CR1501newSHG</t>
   </si>
   <si>
     <t>1000001</t>
@@ -191,22 +182,388 @@
     <t>01-04-2026</t>
   </si>
   <si>
-    <t>100000</t>
+    <t>40001</t>
+  </si>
+  <si>
+    <t>100001</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>AQPPL2144K</t>
+  </si>
+  <si>
+    <t>1234567802</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>CR702</t>
+  </si>
+  <si>
+    <t>123 Main Street</t>
+  </si>
+  <si>
+    <t>SBIN0001234</t>
+  </si>
+  <si>
+    <t>CR1502newSHG</t>
+  </si>
+  <si>
+    <t>1000002</t>
+  </si>
+  <si>
+    <t>40002</t>
+  </si>
+  <si>
+    <t>100002</t>
+  </si>
+  <si>
+    <t>AQPPL5</t>
+  </si>
+  <si>
+    <t>CR703</t>
+  </si>
+  <si>
+    <t>CR1503newSHG</t>
+  </si>
+  <si>
+    <t>1000003</t>
+  </si>
+  <si>
+    <t>40003</t>
+  </si>
+  <si>
+    <t>100003</t>
   </si>
   <si>
     <t>AQPPL2141K</t>
   </si>
   <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>651</t>
-  </si>
-  <si>
-    <t>SHG01234666</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1234567804</t>
+  </si>
+  <si>
+    <t>CR704</t>
+  </si>
+  <si>
+    <t>CR1504newSHG</t>
+  </si>
+  <si>
+    <t>1000004</t>
+  </si>
+  <si>
+    <t>40004</t>
+  </si>
+  <si>
+    <t>100004</t>
+  </si>
+  <si>
+    <t>CR705</t>
+  </si>
+  <si>
+    <t>CR1505newSHG</t>
+  </si>
+  <si>
+    <t>1000005</t>
+  </si>
+  <si>
+    <t>40005</t>
+  </si>
+  <si>
+    <t>100005</t>
+  </si>
+  <si>
+    <t>CR706</t>
+  </si>
+  <si>
+    <t>CR1506newSHG</t>
+  </si>
+  <si>
+    <t>1000006</t>
+  </si>
+  <si>
+    <t>40006</t>
+  </si>
+  <si>
+    <t>100006</t>
+  </si>
+  <si>
+    <t>CR707</t>
+  </si>
+  <si>
+    <t>CR1507newSHG</t>
+  </si>
+  <si>
+    <t>1000007</t>
+  </si>
+  <si>
+    <t>40007</t>
+  </si>
+  <si>
+    <t>100007</t>
+  </si>
+  <si>
+    <t>CR708</t>
+  </si>
+  <si>
+    <t>CR1508newSHG</t>
+  </si>
+  <si>
+    <t>1000008</t>
+  </si>
+  <si>
+    <t>40008</t>
+  </si>
+  <si>
+    <t>100008</t>
+  </si>
+  <si>
+    <t>CR709</t>
+  </si>
+  <si>
+    <t>CR1509newSHG</t>
+  </si>
+  <si>
+    <t>1000009</t>
+  </si>
+  <si>
+    <t>40009</t>
+  </si>
+  <si>
+    <t>100009</t>
+  </si>
+  <si>
+    <t>CR710</t>
+  </si>
+  <si>
+    <t>CR1510newSHG</t>
+  </si>
+  <si>
+    <t>1000010</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>100010</t>
+  </si>
+  <si>
+    <t>CR711</t>
+  </si>
+  <si>
+    <t>CR1511newSHG</t>
+  </si>
+  <si>
+    <t>1000011</t>
+  </si>
+  <si>
+    <t>40011</t>
+  </si>
+  <si>
+    <t>100011</t>
+  </si>
+  <si>
+    <t>CR712</t>
+  </si>
+  <si>
+    <t>CR1512newSHG</t>
+  </si>
+  <si>
+    <t>1000012</t>
+  </si>
+  <si>
+    <t>40012</t>
+  </si>
+  <si>
+    <t>100012</t>
+  </si>
+  <si>
+    <t>CR713</t>
+  </si>
+  <si>
+    <t>CR1513newSHG</t>
+  </si>
+  <si>
+    <t>1000013</t>
+  </si>
+  <si>
+    <t>40013</t>
+  </si>
+  <si>
+    <t>100013</t>
+  </si>
+  <si>
+    <t>CR714</t>
+  </si>
+  <si>
+    <t>CR1514newSHG</t>
+  </si>
+  <si>
+    <t>1000014</t>
+  </si>
+  <si>
+    <t>40014</t>
+  </si>
+  <si>
+    <t>100014</t>
+  </si>
+  <si>
+    <t>CR715</t>
+  </si>
+  <si>
+    <t>CR1515newSHG</t>
+  </si>
+  <si>
+    <t>1000015</t>
+  </si>
+  <si>
+    <t>40015</t>
+  </si>
+  <si>
+    <t>100015</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>CR716</t>
+  </si>
+  <si>
+    <t>CR1516newSHG</t>
+  </si>
+  <si>
+    <t>1000016</t>
+  </si>
+  <si>
+    <t>40016</t>
+  </si>
+  <si>
+    <t>100016</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CR717</t>
+  </si>
+  <si>
+    <t>CR1517newSHG</t>
+  </si>
+  <si>
+    <t>1000017</t>
+  </si>
+  <si>
+    <t>40017</t>
+  </si>
+  <si>
+    <t>100017</t>
+  </si>
+  <si>
+    <t>CR718</t>
+  </si>
+  <si>
+    <t>CR1518newSHG</t>
+  </si>
+  <si>
+    <t>1000018</t>
+  </si>
+  <si>
+    <t>40018</t>
+  </si>
+  <si>
+    <t>100018</t>
+  </si>
+  <si>
+    <t>CR719</t>
+  </si>
+  <si>
+    <t>CR1519newSHG</t>
+  </si>
+  <si>
+    <t>1000019</t>
+  </si>
+  <si>
+    <t>40019</t>
+  </si>
+  <si>
+    <t>100019</t>
+  </si>
+  <si>
+    <t>CR720</t>
+  </si>
+  <si>
+    <t>CR1520newSHG</t>
+  </si>
+  <si>
+    <t>1000020</t>
+  </si>
+  <si>
+    <t>40020</t>
+  </si>
+  <si>
+    <t>100020</t>
+  </si>
+  <si>
+    <t>CR721</t>
+  </si>
+  <si>
+    <t>CR1521newSHG</t>
+  </si>
+  <si>
+    <t>1000021</t>
+  </si>
+  <si>
+    <t>40021</t>
+  </si>
+  <si>
+    <t>100021</t>
+  </si>
+  <si>
+    <t>CR722</t>
+  </si>
+  <si>
+    <t>CR1522newSHG</t>
+  </si>
+  <si>
+    <t>1000022</t>
+  </si>
+  <si>
+    <t>40022</t>
+  </si>
+  <si>
+    <t>100022</t>
+  </si>
+  <si>
+    <t>CR723</t>
+  </si>
+  <si>
+    <t>CR1523newSHG</t>
+  </si>
+  <si>
+    <t>1000023</t>
+  </si>
+  <si>
+    <t>40023</t>
+  </si>
+  <si>
+    <t>100023</t>
+  </si>
+  <si>
+    <t>CR724</t>
+  </si>
+  <si>
+    <t>CR1524newSHG</t>
+  </si>
+  <si>
+    <t>1000024</t>
+  </si>
+  <si>
+    <t>40024</t>
+  </si>
+  <si>
+    <t>100024</t>
   </si>
 </sst>
 </file>
@@ -380,12 +737,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -574,45 +949,10 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -739,7 +1079,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -751,133 +1091,153 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1228,8 +1588,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:AN25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="18.5714285714286" customWidth="1"/>
@@ -1249,14 +1609,14 @@
     <col min="16" max="16" width="20.2857142857143" customWidth="1"/>
     <col min="17" max="17" width="21.7142857142857" customWidth="1"/>
     <col min="18" max="18" width="16.8571428571429" customWidth="1"/>
-    <col min="19" max="19" width="16.1428571428571" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="13.8571428571429" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1428571428571" style="6" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
+    <col min="21" max="21" width="13.8571428571429" style="6" customWidth="1"/>
     <col min="22" max="22" width="14.8571428571429" customWidth="1"/>
     <col min="23" max="23" width="9.42857142857143" customWidth="1"/>
-    <col min="24" max="24" width="15" style="1" customWidth="1"/>
+    <col min="24" max="24" width="15" style="6" customWidth="1"/>
     <col min="25" max="25" width="8.57142857142857" customWidth="1"/>
-    <col min="26" max="26" width="10.4285714285714" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.4285714285714" style="6" customWidth="1"/>
     <col min="27" max="27" width="6.85714285714286" customWidth="1"/>
     <col min="28" max="28" width="8.85714285714286" customWidth="1"/>
     <col min="29" max="29" width="11.8571428571429" customWidth="1"/>
@@ -1273,115 +1633,115 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:40">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AI1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="10" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
@@ -1395,218 +1755,2598 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:40">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="11">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="11">
         <v>209</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="11">
+        <v>233</v>
+      </c>
+      <c r="M2" s="11">
+        <v>10</v>
+      </c>
+      <c r="N2" s="11">
+        <v>800026</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="P2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="2">
-        <v>800026</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="U2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="W2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="AC2" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" s="7">
-        <v>1000</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="7">
-        <v>1234567893</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AK2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AK2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN2" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:40">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="11">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="11">
+        <v>209</v>
+      </c>
+      <c r="L3" s="11">
+        <v>233</v>
+      </c>
+      <c r="M3" s="11">
+        <v>10</v>
+      </c>
+      <c r="N3" s="11">
+        <v>800026</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC3" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN3" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:40">
+      <c r="A4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="11">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="11">
+        <v>209</v>
+      </c>
+      <c r="L4" s="11">
+        <v>233</v>
+      </c>
+      <c r="M4" s="11">
+        <v>10</v>
+      </c>
+      <c r="N4" s="11">
+        <v>800026</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC4" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN4" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:40">
+      <c r="A5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K5" s="11">
         <v>209</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="2">
+      <c r="L5" s="11">
+        <v>233</v>
+      </c>
+      <c r="M5" s="11">
+        <v>10</v>
+      </c>
+      <c r="N5" s="11">
         <v>800026</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="O5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC5" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:40">
+      <c r="A6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="11">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="R3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="2" t="s">
+      <c r="K6" s="11">
+        <v>209</v>
+      </c>
+      <c r="L6" s="11">
+        <v>233</v>
+      </c>
+      <c r="M6" s="11">
+        <v>10</v>
+      </c>
+      <c r="N6" s="11">
+        <v>800026</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="AC6" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN6" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:40">
+      <c r="A7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="11">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="11">
+        <v>209</v>
+      </c>
+      <c r="L7" s="11">
+        <v>233</v>
+      </c>
+      <c r="M7" s="11">
+        <v>10</v>
+      </c>
+      <c r="N7" s="11">
+        <v>800026</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN7" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:40">
+      <c r="A8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="14">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="14">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="14">
+        <v>209</v>
+      </c>
+      <c r="L8" s="14">
+        <v>233</v>
+      </c>
+      <c r="M8" s="14">
+        <v>10</v>
+      </c>
+      <c r="N8" s="14">
+        <v>800026</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC8" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN8" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:40">
+      <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="14">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="14">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="14">
+        <v>209</v>
+      </c>
+      <c r="L9" s="14">
+        <v>233</v>
+      </c>
+      <c r="M9" s="14">
+        <v>10</v>
+      </c>
+      <c r="N9" s="14">
+        <v>800026</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="R9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="7">
-        <v>1000</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN9" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:40">
+      <c r="A10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="14">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="14">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="14">
+        <v>209</v>
+      </c>
+      <c r="L10" s="14">
+        <v>233</v>
+      </c>
+      <c r="M10" s="14">
+        <v>10</v>
+      </c>
+      <c r="N10" s="14">
+        <v>800026</v>
+      </c>
+      <c r="O10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="P10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC10" s="14">
         <v>0</v>
       </c>
-      <c r="AD3" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AD10" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN10" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:40">
+      <c r="A11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="14">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="14">
+        <v>209</v>
+      </c>
+      <c r="L11" s="14">
+        <v>233</v>
+      </c>
+      <c r="M11" s="14">
+        <v>10</v>
+      </c>
+      <c r="N11" s="14">
+        <v>800026</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="W11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC11" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AI3" s="7">
-        <v>1234567893</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ11" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AK11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN11" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:40">
+      <c r="A12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="14">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="14">
+        <v>209</v>
+      </c>
+      <c r="L12" s="14">
+        <v>233</v>
+      </c>
+      <c r="M12" s="14">
+        <v>10</v>
+      </c>
+      <c r="N12" s="14">
+        <v>800026</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="W12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC12" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN12" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:40">
+      <c r="A13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="16">
+        <v>1</v>
+      </c>
+      <c r="D13" s="16">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="16">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="16">
+        <v>209</v>
+      </c>
+      <c r="L13" s="16">
+        <v>233</v>
+      </c>
+      <c r="M13" s="16">
+        <v>10</v>
+      </c>
+      <c r="N13" s="16">
+        <v>800026</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="S13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="U13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="W13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC13" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="16">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM13" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN13" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" spans="1:40">
+      <c r="A14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="18">
+        <v>1</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="18">
+        <v>209</v>
+      </c>
+      <c r="L14" s="18">
+        <v>233</v>
+      </c>
+      <c r="M14" s="18">
+        <v>10</v>
+      </c>
+      <c r="N14" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="W14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="18"/>
+      <c r="AB14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC14" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF14" s="18"/>
+      <c r="AG14" s="18"/>
+      <c r="AH14" s="18"/>
+      <c r="AI14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN14" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" s="5" customFormat="1" spans="1:40">
+      <c r="A15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="18">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="18">
+        <v>1</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" s="18">
+        <v>209</v>
+      </c>
+      <c r="L15" s="18">
+        <v>233</v>
+      </c>
+      <c r="M15" s="18">
+        <v>10</v>
+      </c>
+      <c r="N15" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="W15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="18"/>
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC15" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF15" s="18"/>
+      <c r="AG15" s="18"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN15" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" s="5" customFormat="1" spans="1:40">
+      <c r="A16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="18">
+        <v>1</v>
+      </c>
+      <c r="D16" s="18">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="18">
+        <v>1</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="18">
+        <v>209</v>
+      </c>
+      <c r="L16" s="18">
+        <v>233</v>
+      </c>
+      <c r="M16" s="18">
+        <v>10</v>
+      </c>
+      <c r="N16" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O16" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" s="18"/>
+      <c r="AA16" s="18"/>
+      <c r="AB16" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC16" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF16" s="18"/>
+      <c r="AG16" s="18"/>
+      <c r="AH16" s="18"/>
+      <c r="AI16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ16" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN16" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="1" spans="1:40">
+      <c r="A17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="18">
+        <v>1</v>
+      </c>
+      <c r="D17" s="18">
+        <v>1</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="18">
+        <v>1</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="18">
+        <v>209</v>
+      </c>
+      <c r="L17" s="18">
+        <v>233</v>
+      </c>
+      <c r="M17" s="18">
+        <v>10</v>
+      </c>
+      <c r="N17" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="W17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC17" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF17" s="18"/>
+      <c r="AG17" s="18"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ17" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN17" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" s="5" customFormat="1" spans="1:40">
+      <c r="A18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="18">
+        <v>209</v>
+      </c>
+      <c r="L18" s="18">
+        <v>233</v>
+      </c>
+      <c r="M18" s="18">
+        <v>10</v>
+      </c>
+      <c r="N18" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="W18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18" s="18"/>
+      <c r="Y18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC18" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF18" s="18"/>
+      <c r="AG18" s="18"/>
+      <c r="AH18" s="18"/>
+      <c r="AI18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ18" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN18" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" s="5" customFormat="1" spans="1:40">
+      <c r="A19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="18">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="18">
+        <v>1</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" s="18">
+        <v>209</v>
+      </c>
+      <c r="L19" s="18">
+        <v>233</v>
+      </c>
+      <c r="M19" s="18">
+        <v>10</v>
+      </c>
+      <c r="N19" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="W19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC19" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF19" s="18"/>
+      <c r="AG19" s="18"/>
+      <c r="AH19" s="18"/>
+      <c r="AI19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ19" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN19" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" s="5" customFormat="1" spans="1:40">
+      <c r="A20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="18">
+        <v>1</v>
+      </c>
+      <c r="D20" s="18">
+        <v>1</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="18">
+        <v>1</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="18">
+        <v>209</v>
+      </c>
+      <c r="L20" s="18">
+        <v>233</v>
+      </c>
+      <c r="M20" s="18">
+        <v>10</v>
+      </c>
+      <c r="N20" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="W20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC20" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF20" s="18"/>
+      <c r="AG20" s="18"/>
+      <c r="AH20" s="18"/>
+      <c r="AI20" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ20" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN20" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" s="5" customFormat="1" spans="1:40">
+      <c r="A21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="18">
+        <v>1</v>
+      </c>
+      <c r="D21" s="18">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="18">
+        <v>1</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="18">
+        <v>209</v>
+      </c>
+      <c r="L21" s="18">
+        <v>233</v>
+      </c>
+      <c r="M21" s="18">
+        <v>10</v>
+      </c>
+      <c r="N21" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="W21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC21" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF21" s="18"/>
+      <c r="AG21" s="18"/>
+      <c r="AH21" s="18"/>
+      <c r="AI21" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN21" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" s="5" customFormat="1" spans="1:40">
+      <c r="A22" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="18">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="18">
+        <v>1</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" s="18">
+        <v>209</v>
+      </c>
+      <c r="L22" s="18">
+        <v>233</v>
+      </c>
+      <c r="M22" s="18">
+        <v>10</v>
+      </c>
+      <c r="N22" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="R22" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="S22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="W22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC22" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF22" s="18"/>
+      <c r="AG22" s="18"/>
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ22" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN22" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" s="5" customFormat="1" spans="1:40">
+      <c r="A23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="18">
+        <v>1</v>
+      </c>
+      <c r="D23" s="18">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="18">
+        <v>1</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="18">
+        <v>209</v>
+      </c>
+      <c r="L23" s="18">
+        <v>233</v>
+      </c>
+      <c r="M23" s="18">
+        <v>10</v>
+      </c>
+      <c r="N23" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="W23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC23" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF23" s="18"/>
+      <c r="AG23" s="18"/>
+      <c r="AH23" s="18"/>
+      <c r="AI23" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ23" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN23" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" s="5" customFormat="1" spans="1:40">
+      <c r="A24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1</v>
+      </c>
+      <c r="D24" s="18">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="18">
+        <v>1</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K24" s="18">
+        <v>209</v>
+      </c>
+      <c r="L24" s="18">
+        <v>233</v>
+      </c>
+      <c r="M24" s="18">
+        <v>10</v>
+      </c>
+      <c r="N24" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="W24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC24" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF24" s="18"/>
+      <c r="AG24" s="18"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ24" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM24" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN24" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" s="5" customFormat="1" spans="1:40">
+      <c r="A25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="18">
+        <v>1</v>
+      </c>
+      <c r="D25" s="18">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="18">
+        <v>1</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="18">
+        <v>209</v>
+      </c>
+      <c r="L25" s="18">
+        <v>233</v>
+      </c>
+      <c r="M25" s="18">
+        <v>10</v>
+      </c>
+      <c r="N25" s="18">
+        <v>800026</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="W25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC25" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="18"/>
+      <c r="AH25" s="18"/>
+      <c r="AI25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ25" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN25" s="18" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN3" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
